--- a/Result/profitability/2884.xlsx
+++ b/Result/profitability/2884.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM98"/>
+  <dimension ref="A1:AM99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
         <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>0.48125</v>
+        <v>0.505</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -766,7 +766,7 @@
         <v>0.31</v>
       </c>
       <c r="M3" t="n">
-        <v>0.45625</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -877,7 +877,7 @@
         <v>0.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0.45875</v>
+        <v>0.4775</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -988,7 +988,7 @@
         <v>-2.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09375</v>
+        <v>0.12</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1099,7 +1099,7 @@
         <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0.10125</v>
+        <v>0.11625</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1218,7 +1218,7 @@
         <v>0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.10375</v>
+        <v>0.12875</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1337,7 +1337,7 @@
         <v>0.63</v>
       </c>
       <c r="M8" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
         <v>0.36</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08749999999999998</v>
+        <v>0.08750000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>33.3575</v>
@@ -1698,7 +1698,7 @@
         <v>0.73</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1924999999999999</v>
+        <v>0.1925</v>
       </c>
       <c r="N11" t="n">
         <v>40.88</v>
@@ -1940,7 +1940,7 @@
         <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5337499999999999</v>
+        <v>0.5337500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>68.91374999999999</v>
@@ -2061,7 +2061,7 @@
         <v>0.49</v>
       </c>
       <c r="M14" t="n">
-        <v>0.52625</v>
+        <v>0.5262500000000001</v>
       </c>
       <c r="N14" t="n">
         <v>68.965</v>
@@ -2303,7 +2303,7 @@
         <v>0.37</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4725</v>
+        <v>0.4725000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>66.08499999999999</v>
@@ -2787,7 +2787,7 @@
         <v>0.28</v>
       </c>
       <c r="M20" t="n">
-        <v>0.25</v>
+        <v>0.2500000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>49.54</v>
@@ -3029,7 +3029,7 @@
         <v>0.26</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1825</v>
+        <v>0.1825000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>44.7625</v>
@@ -3150,7 +3150,7 @@
         <v>0.28</v>
       </c>
       <c r="M23" t="n">
-        <v>0.16375</v>
+        <v>0.1637500000000001</v>
       </c>
       <c r="N23" t="n">
         <v>42.34875</v>
@@ -3271,7 +3271,7 @@
         <v>0.31</v>
       </c>
       <c r="M24" t="n">
-        <v>0.15625</v>
+        <v>0.1562500000000001</v>
       </c>
       <c r="N24" t="n">
         <v>41.12125</v>
@@ -3392,7 +3392,7 @@
         <v>0.14</v>
       </c>
       <c r="M25" t="n">
-        <v>0.14</v>
+        <v>0.1400000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>39.74</v>
@@ -3505,7 +3505,7 @@
         <v>0.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0.135</v>
+        <v>0.1350000000000001</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
@@ -3612,7 +3612,7 @@
         <v>0.1</v>
       </c>
       <c r="M27" t="n">
-        <v>0.22625</v>
+        <v>0.2262500000000001</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
@@ -3719,7 +3719,7 @@
         <v>0.21</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2175</v>
+        <v>0.2175000000000001</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
@@ -3826,7 +3826,7 @@
         <v>-0.25</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1625</v>
+        <v>0.1625000000000001</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
@@ -3933,7 +3933,7 @@
         <v>0.17</v>
       </c>
       <c r="M30" t="n">
-        <v>0.15125</v>
+        <v>0.1512500000000001</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
@@ -4040,7 +4040,7 @@
         <v>0.08</v>
       </c>
       <c r="M31" t="n">
-        <v>0.12625</v>
+        <v>0.1262500000000001</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
@@ -4147,7 +4147,7 @@
         <v>0.16</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1075</v>
+        <v>0.1075000000000001</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
@@ -4254,7 +4254,7 @@
         <v>0.13</v>
       </c>
       <c r="M33" t="n">
-        <v>0.10625</v>
+        <v>0.1062500000000001</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
@@ -4361,7 +4361,7 @@
         <v>0.29</v>
       </c>
       <c r="M34" t="n">
-        <v>0.11125</v>
+        <v>0.1112500000000001</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
@@ -4468,7 +4468,7 @@
         <v>0.3</v>
       </c>
       <c r="M35" t="n">
-        <v>0.13625</v>
+        <v>0.1362500000000001</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
@@ -4575,7 +4575,7 @@
         <v>0.25</v>
       </c>
       <c r="M36" t="n">
-        <v>0.14125</v>
+        <v>0.1412500000000001</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
@@ -4682,7 +4682,7 @@
         <v>0.23</v>
       </c>
       <c r="M37" t="n">
-        <v>0.20125</v>
+        <v>0.2012500000000001</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
@@ -11272,6 +11272,113 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>28674</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="n">
+        <v>14063</v>
+      </c>
+      <c r="K99" t="n">
+        <v>11377</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.5349999999999999</v>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="n">
+        <v>1</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1</v>
+      </c>
+      <c r="V99" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0.07999999999999996</v>
+      </c>
+      <c r="X99" t="n">
+        <v>0.129032258064516</v>
+      </c>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK99" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
